--- a/data/trans_bre/IP43-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP43-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 1,97</t>
+          <t>-21,3; 1,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 8,88</t>
+          <t>-12,32; 9,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-69,74; 9,78</t>
+          <t>-70,29; 13,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,37; 82,12</t>
+          <t>-56,72; 82,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 1,09</t>
+          <t>-14,99; 2,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,0</t>
+          <t>-3,47; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 8,37</t>
+          <t>-60,21; 17,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,0</t>
+          <t>-5,75; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 12,51</t>
+          <t>-4,45; 12,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 19,2</t>
+          <t>2,99; 20,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 276,14</t>
+          <t>-44,05; 278,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,93; 604,03</t>
+          <t>12,61; 671,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 15,97</t>
+          <t>-13,19; 15,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 23,58</t>
+          <t>-10,25; 22,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 21,96</t>
+          <t>-15,6; 21,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 117,0</t>
+          <t>-28,55; 112,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,0</t>
+          <t>-4,27; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 1,24</t>
+          <t>-11,04; 1,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 3,49</t>
+          <t>-4,65; 3,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 2,38</t>
+          <t>-4,85; 2,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 143,09</t>
+          <t>-69,33; 149,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-89,26; 207,73</t>
+          <t>-88,78; 158,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 11,35</t>
+          <t>-5,21; 11,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 8,21</t>
+          <t>-6,99; 9,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 24,31</t>
+          <t>-9,31; 25,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 34,58</t>
+          <t>-21,95; 39,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,81</t>
+          <t>-4,12; 3,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,6</t>
+          <t>-1,72; 3,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 13,21</t>
+          <t>-16,38; 13,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 35,85</t>
+          <t>-13,83; 35,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
